--- a/VerveStacks_ESP_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ESP_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F491597-7EDF-4DDA-8770-70456FEF2711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{753CA500-F3DF-45EC-98B6-8C0299CFC156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5F241A92-50C8-4D2F-B2D5-96B6C5D4B790}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{644BE8AB-E50C-4DBE-8F78-1CFCE694D48C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2653,7 +2653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{508DDE2E-A3A6-4D37-B38E-44C22A7D1A91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54E8500C-CD2E-45E8-B8F2-97031AA748CC}">
   <dimension ref="B3:L344"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
